--- a/GPS-Ecosystem.xlsx
+++ b/GPS-Ecosystem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scdoe-my.sharepoint.com/personal/wcothran_ed_sc_gov/Documents/Delete/Claude_Code/gps-ecosystem-visual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E97CDB31-AE9D-4C9A-89D9-7D4DBC6C9518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8237F00A-02C2-4098-8E01-E522D7C73EAC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC28435E-64FB-4656-9708-077C6C3C2A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6126C415-B466-49E1-AF6D-20CC7A56C3B7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{43B4E3D6-EC6B-4AF6-BCA7-EFB295CB23B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="141">
   <si>
     <t>Section</t>
   </si>
@@ -57,6 +57,12 @@
     <t>Future</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Flow</t>
+  </si>
+  <si>
     <t>Dashboards</t>
   </si>
   <si>
@@ -111,16 +117,28 @@
     <t>Student-level decision-support app for classroom teachers. Student, Classroom, Grade Level, and Section disaggregations of student performance dashboards. Expected growth projections for students; grouping feature for interventions.</t>
   </si>
   <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
     <t>Student View; Class View; Grade View; Group View</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/teacher-navigator-2026-05-05.docx</t>
+  </si>
+  <si>
     <t>Admin Navigator</t>
   </si>
   <si>
     <t>School and district leader app with aggregate data and drill-down dashboards. Allows for analysis of enrollment, attendance, behavior, assessments, grades, and accountability indicators.</t>
   </si>
   <si>
-    <t>https://scdoe.sharepoint.com/:w:/s/X-TeamGPSGrowingPathwaysforStudents_Group/IQBu-joU23DHT4uYeTMIV_9_AbUuGDtnaZ08lrJPb-vsaM0?e=OoI1nh</t>
+    <t>Profile; Chronic Absenteeism; Enrollment; Behavior; Assessment; Course Grades; On-Track &amp; CCR; Predictions</t>
+  </si>
+  <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/administrator-navigator-2026-05-05.docx</t>
   </si>
   <si>
     <t>PDC Dashboards</t>
@@ -132,6 +150,9 @@
     <t>District-facing analytics dashboards delivered by the Palmetto Data Collaborative (PDC). Separate product from the Navigators - uses the same data foundation but accessed by LEA staff for ad-hoc and comparative visualizations.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/podium-plus-2026-05-05.docx</t>
+  </si>
+  <si>
     <t>Member Center</t>
   </si>
   <si>
@@ -141,6 +162,9 @@
     <t>App portal for SCDE and LEA users. Content spans HR functions and Grant Reporting to Data Reports and Support Requests.</t>
   </si>
   <si>
+    <t>Bidirectional</t>
+  </si>
+  <si>
     <t>Outputs</t>
   </si>
   <si>
@@ -150,30 +174,48 @@
     <t>School accountability reports published annually.</t>
   </si>
   <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/school-report-cards.docx</t>
+  </si>
+  <si>
     <t>Funding Data</t>
   </si>
   <si>
     <t>Financial and funding visualizations and reports, driven by GPS analytics.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/funding-data.docx</t>
+  </si>
+  <si>
     <t>Research Requests</t>
   </si>
   <si>
     <t>Custom data extracts for approved external research partners and policy studies.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/research-requests.docx</t>
+  </si>
+  <si>
     <t>Program Office Reports</t>
   </si>
   <si>
     <t>Aggregated analytics (reports and visualizations) consumed by SCDE program offices for program management, evaluations, and federal reporting.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/program-office-reports-and-analytics.docx</t>
+  </si>
+  <si>
     <t>App Platform</t>
   </si>
   <si>
     <t>A planned app-store model: vetted SCDE offices or partners publish data services on the GPS platform.</t>
   </si>
   <si>
+    <t>Service</t>
+  </si>
+  <si>
     <t>State Navigator</t>
   </si>
   <si>
@@ -189,6 +231,12 @@
     <t>Single sign-on and rostering provider. Pushes identity/roster data into connected apps.</t>
   </si>
   <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/classlink-statelink.docx</t>
+  </si>
+  <si>
     <t>Palmetto Pathways</t>
   </si>
   <si>
@@ -198,24 +246,36 @@
     <t>Student graduation pathways and credential tracking application. Includes workflows for school counselors and school/district administrators.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/palmetto-pathways.docx</t>
+  </si>
+  <si>
     <t>GiftED</t>
   </si>
   <si>
     <t>Gifted and talented program-management service. Sends program eligibility and participation data into GPS.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/gifted.docx</t>
+  </si>
+  <si>
     <t>Everyday Labs</t>
   </si>
   <si>
     <t>Attendance intervention partner. Consumes attendance data from GPS and delivers attendance recovery interventions to schools.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/everyday-labs.docx</t>
+  </si>
+  <si>
     <t>EdPlan SC</t>
   </si>
   <si>
     <t>Individualized Education Plan (IEP) management service. Bi-directional data exchange with GPS.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/edplan-sc.docx</t>
+  </si>
+  <si>
     <t>Assessment Rostering</t>
   </si>
   <si>
@@ -231,6 +291,9 @@
     <t>Statewide Student Information System - the canonical source for enrollment, demographics, grades, attendance, and schedules. PowerSchool is an external vendor system integrated with the Ed-Fi API.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/powerschool-sis.docx</t>
+  </si>
+  <si>
     <t>Students Assessments</t>
   </si>
   <si>
@@ -249,12 +312,18 @@
     <t>Diagnostic and instructional assessment data from district adoptions of iReady.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/iready.docx</t>
+  </si>
+  <si>
     <t>Early Childhood Programs</t>
   </si>
   <si>
     <t>Early childhood program enrollment and outcomes data.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/early-childhood-program-data.docx</t>
+  </si>
+  <si>
     <t>ESTF Data</t>
   </si>
   <si>
@@ -291,6 +360,9 @@
     <t>The centralized cloud longitudinal data warehouse where all GPS data lands and is analytically modeled.</t>
   </si>
   <si>
+    <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/stadium-2026-05-05.docx</t>
+  </si>
+  <si>
     <t>Ed-Fi Integration Layer</t>
   </si>
   <si>
@@ -391,9 +463,6 @@
   </si>
   <si>
     <t>Who keeps the ecosystem coherent across SCDE divisions and partners.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Profile; Chronic Absenteeism; Enrollment; Behavior; Assessment; Course Grades; On-Track &amp; CCR; PreAccountability; On-Track; College &amp; Career Readiness; Attendance; Growth &amp; Predicted Growth; Accountability Metric Comparisons; Accountability Predictions &amp; Targets; Section Profile </t>
   </si>
 </sst>
 </file>
@@ -791,21 +860,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E518B1-1318-4B6E-B6C8-CF66F4009913}">
-  <dimension ref="A1:H37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777012E0-1208-432C-A6B6-93E941CA41DE}">
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
     <col min="2" max="2" width="28.6328125" customWidth="1"/>
     <col min="3" max="3" width="18.6328125" customWidth="1"/>
-    <col min="4" max="4" width="80.6328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="40.6328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="50.6328125" customWidth="1"/>
-    <col min="8" max="8" width="8.6328125" customWidth="1"/>
+    <col min="4" max="4" width="70.6328125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="9.6328125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="8" max="8" width="40.6328125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="50.6328125" customWidth="1"/>
+    <col min="10" max="10" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -821,683 +891,896 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
+    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
         <v>25</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
-      <c r="H8">
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
-      <c r="H12">
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="H14">
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
-      <c r="H15">
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
-      <c r="H16">
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
-      <c r="H17">
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
-      <c r="H18">
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
         <v>57</v>
       </c>
-      <c r="E20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="G21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="H28">
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
+        <v>63</v>
+      </c>
+      <c r="J28">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="H29">
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
-      <c r="H30">
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>63</v>
+      </c>
+      <c r="J30">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
-      <c r="H31">
+      <c r="I31" t="s">
+        <v>106</v>
+      </c>
+      <c r="J31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid section" error="Pick one of: Audiences,Tools &amp; Apps,Data Services,Foundation,Governance,Outputs,Inputs" sqref="A2:A500" xr:uid="{4FE4773C-04C0-419F-BE92-3152DC736A77}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid section" error="Pick one of: Audiences,Tools &amp; Apps,Data Services,Foundation,Governance,Outputs,Inputs" sqref="A2:A500" xr:uid="{D3942D76-DB98-4DDA-B1ED-7D9D9D007EA8}">
       <formula1>"Audiences,Tools &amp; Apps,Data Services,Foundation,Governance,Outputs,Inputs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E500" xr:uid="{4B227FD9-4EEB-47DB-B65F-E75A6AD2F22E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E500" xr:uid="{A7B6A5E7-8C0E-47C5-9B22-F634DC1D5382}">
       <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid type" error="Pick one of: App,Data,Service (or leave blank)" sqref="F2:F500" xr:uid="{4C07042B-B362-4EE2-8076-98F9ACBA0193}">
+      <formula1>"App,Data,Service"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid flow" error="Pick one of: In,Out,Bidirectional (or leave blank)" sqref="G2:G500" xr:uid="{0DB5241B-AE52-444B-8143-8DABE18E1959}">
+      <formula1>"In,Out,Bidirectional"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1505,7 +1788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABF28DE-9E70-4103-BBBC-4DBF035B4AAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D5FF8D-F052-4BFE-B33D-61B939EB278A}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1515,74 +1798,74 @@
   <sheetData>
     <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/GPS-Ecosystem.xlsx
+++ b/GPS-Ecosystem.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scdoe-my.sharepoint.com/personal/wcothran_ed_sc_gov/Documents/Delete/Claude_Code/gps-ecosystem-visual/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared Documents/General/04_GPS Inventory/_ecosystem visual html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC28435E-64FB-4656-9708-077C6C3C2A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{BC28435E-64FB-4656-9708-077C6C3C2A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CE654AA-D24D-4D14-A912-9FB21780A7B5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{43B4E3D6-EC6B-4AF6-BCA7-EFB295CB23B8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="137">
   <si>
     <t>Section</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Bidirectional</t>
   </si>
   <si>
-    <t>Outputs</t>
-  </si>
-  <si>
     <t>School Report Cards</t>
   </si>
   <si>
@@ -180,9 +177,6 @@
     <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/school-report-cards.docx</t>
   </si>
   <si>
-    <t>Funding Data</t>
-  </si>
-  <si>
     <t>Financial and funding visualizations and reports, driven by GPS analytics.</t>
   </si>
   <si>
@@ -207,9 +201,6 @@
     <t>https://scdoe.sharepoint.com/sites/X-TeamGPSGrowingPathwaysforStudents_Group/Shared%20Documents/General/04_GPS%20Inventory/program-office-reports-and-analytics.docx</t>
   </si>
   <si>
-    <t>App Platform</t>
-  </si>
-  <si>
     <t>A planned app-store model: vetted SCDE offices or partners publish data services on the GPS platform.</t>
   </si>
   <si>
@@ -300,12 +291,6 @@
     <t>Student assessment results (SC READY, SC PASS, end-of-course, etc.) loaded into GPS for analytics.</t>
   </si>
   <si>
-    <t>EdPlanSC</t>
-  </si>
-  <si>
-    <t>Individualized Education Plan (IEP) management service. Note: EdPlanSC also appears as a Data Service because it both produces and consumes data.</t>
-  </si>
-  <si>
     <t>iReady</t>
   </si>
   <si>
@@ -463,6 +448,9 @@
   </si>
   <si>
     <t>Who keeps the ecosystem coherent across SCDE divisions and partners.</t>
+  </si>
+  <si>
+    <t>GPS App Platform</t>
   </si>
 </sst>
 </file>
@@ -861,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777012E0-1208-432C-A6B6-93E941CA41DE}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
@@ -1016,7 +1004,7 @@
         <v>28</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -1048,7 +1036,7 @@
         <v>32</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -1077,7 +1065,7 @@
         <v>36</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -1103,145 +1091,145 @@
         <v>40</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>48</v>
-      </c>
       <c r="J11">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
         <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
       </c>
       <c r="I13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
         <v>40</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -1253,43 +1241,43 @@
         <v>26</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
         <v>66</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -1308,12 +1296,12 @@
         <v>68</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>69</v>
@@ -1325,21 +1313,21 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
         <v>71</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>72</v>
@@ -1351,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
         <v>40</v>
@@ -1360,18 +1348,18 @@
         <v>74</v>
       </c>
       <c r="J19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -1383,403 +1371,377 @@
         <v>40</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>57</v>
       </c>
-      <c r="G21" t="s">
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" t="s">
         <v>40</v>
       </c>
-      <c r="I21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21">
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22">
         <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" t="s">
-        <v>63</v>
-      </c>
-      <c r="I22" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" t="s">
-        <v>90</v>
-      </c>
       <c r="J25">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" t="s">
-        <v>63</v>
-      </c>
-      <c r="I26" t="s">
-        <v>93</v>
-      </c>
-      <c r="J26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
         <v>101</v>
       </c>
-      <c r="E30" t="b">
+      <c r="J30">
         <v>1</v>
       </c>
-      <c r="F30" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" t="s">
-        <v>63</v>
-      </c>
-      <c r="J30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>103</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" t="s">
         <v>105</v>
       </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="C32" t="s">
         <v>106</v>
       </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="D32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s">
         <v>116</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D36" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid section" error="Pick one of: Audiences,Tools &amp; Apps,Data Services,Foundation,Governance,Outputs,Inputs" sqref="A2:A500" xr:uid="{D3942D76-DB98-4DDA-B1ED-7D9D9D007EA8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid section" error="Pick one of: Audiences,Tools &amp; Apps,Data Services,Foundation,Governance,Outputs,Inputs" sqref="A2:A499" xr:uid="{D3942D76-DB98-4DDA-B1ED-7D9D9D007EA8}">
       <formula1>"Audiences,Tools &amp; Apps,Data Services,Foundation,Governance,Outputs,Inputs"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E500" xr:uid="{A7B6A5E7-8C0E-47C5-9B22-F634DC1D5382}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E499" xr:uid="{A7B6A5E7-8C0E-47C5-9B22-F634DC1D5382}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid type" error="Pick one of: App,Data,Service (or leave blank)" sqref="F2:F500" xr:uid="{4C07042B-B362-4EE2-8076-98F9ACBA0193}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid type" error="Pick one of: App,Data,Service (or leave blank)" sqref="F2:F499" xr:uid="{4C07042B-B362-4EE2-8076-98F9ACBA0193}">
       <formula1>"App,Data,Service"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid flow" error="Pick one of: In,Out,Bidirectional (or leave blank)" sqref="G2:G500" xr:uid="{0DB5241B-AE52-444B-8143-8DABE18E1959}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid flow" error="Pick one of: In,Out,Bidirectional (or leave blank)" sqref="G2:G499" xr:uid="{0DB5241B-AE52-444B-8143-8DABE18E1959}">
       <formula1>"In,Out,Bidirectional"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1798,77 +1760,324 @@
   <sheetData>
     <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100649D2FA1D506C3468CA3E5D6AFC0422E" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d84f4d1776bf24cff4b53865880fd56d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4f88ac18-ee79-4760-827e-2e717126ad72" xmlns:ns3="41cdd203-aec9-4842-99df-5c78e4429b7a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="35afc8eb73ac103b043622eb4bb15a1d" ns2:_="" ns3:_="">
+    <xsd:import namespace="4f88ac18-ee79-4760-827e-2e717126ad72"/>
+    <xsd:import namespace="41cdd203-aec9-4842-99df-5c78e4429b7a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4f88ac18-ee79-4760-827e-2e717126ad72" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0e4daac4-fd0c-4c4b-a426-489ddec535ad" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="41cdd203-aec9-4842-99df-5c78e4429b7a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{70fc819e-4f74-4829-b1ea-e76ae61c9dac}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="41cdd203-aec9-4842-99df-5c78e4429b7a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f88ac18-ee79-4760-827e-2e717126ad72">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="41cdd203-aec9-4842-99df-5c78e4429b7a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A31DD7F-7BCB-4520-B54A-BF92ABCE1883}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4f88ac18-ee79-4760-827e-2e717126ad72"/>
+    <ds:schemaRef ds:uri="41cdd203-aec9-4842-99df-5c78e4429b7a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D3109DD-FB43-4754-A7FC-7244CDDAF16D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4f88ac18-ee79-4760-827e-2e717126ad72"/>
+    <ds:schemaRef ds:uri="41cdd203-aec9-4842-99df-5c78e4429b7a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17D829F7-7A5E-4B29-9998-1DDEC2902B85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>